--- a/data/google_news_dedup_audit_08_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_08_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7398277521133423</v>
+        <v>1.000000238418579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Levi Strauss lifts annual forecasts as strong demand cushions tariff hit - Reuters</t>
+          <t>Levi Strauss raises annual forecasts on resilient demand for premium jeans - MSN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -466,505 +466,106 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7508076429367065</v>
+        <v>0.8715298175811768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Uber scales on AWS to help power millions of daily trips and train its AI models - About Amazon</t>
+          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Uber leverages Amazon AI in delivery and rideshare infrastructure - Chain Store Age</t>
+          <t>Man stabbed to death at Primrose Hill viewpoint - ITVX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9631192684173584</v>
+        <v>0.7428274154663086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after making delivery at her Texas home - CNN</t>
+          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after making delivery at her Texas home - KETV</t>
+          <t>Man, 21, killed at Primrose Hill beauty spot as crowds enjoy sunshine - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9458257555961609</v>
+        <v>0.7217569351196289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after making delivery at her Texas home - CNN</t>
+          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Former FedEx driver pleads guilty to killing 7-year-old girl after making delivery at her Texas home - The Tribune-Democrat</t>
+          <t>Forensics at London viewpoint after man killed and another injured in double stabbing - London Now</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7696876525878906</v>
+        <v>0.5928287506103516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Twee verdachten opgepakt voor steekpartij in Antwerpse stationsbuurt, slachtoffer (17) buiten levensgevaar - VRT</t>
+          <t>Two dead after separate double stabbings just hours apart in London - The Independent</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jongen (17) niet langer in levensgevaar na steekpartij in Antwerpen: twee verdachten opgepakt - HLN</t>
+          <t>Police launch murder investigation as man dies after double stabbing in Shadwell - East London Advertiser</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7250726222991943</v>
+        <v>0.7116384506225586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Twee verdachten opgepakt voor steekpartij in Antwerpse stationsbuurt, slachtoffer (17) buiten levensgevaar - VRT</t>
+          <t>Sanità lombarda, il diritto alla cura passa da chi cura: l’11 aprile in piazza a Milano - FP CGIL Lombardia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jongen (17) niet langer in levensgevaar na steekpartij in Antwerpen: twee verdachten opgepakt | Foto - pzc.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B8" t="n">
-        <v>33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7505258321762085</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Twee verdachten opgepakt voor steekpartij in Antwerpse stationsbuurt, slachtoffer (17) buiten levensgevaar - VRT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Slachtoffer (17) steekpartij Antwerpse Carnotstraat buiten levensgevaar, twee verdachten gearresteerd - Nieuwsblad</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>35</v>
-      </c>
-      <c r="B9" t="n">
-        <v>38</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.000000238418579</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Dramatic footage of gunfight outside Israeli consulate in Istanbul; Attackers shot dead on the spot - The Economic Times</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Dramatic footage of gunfight outside Israeli consulate in Istanbul; Attackers shot dead on the spot - The Economic Times</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B10" t="n">
-        <v>45</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7255892753601074</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FIU graduate programs rank among nation’s top 50 public programs, led by No. 5 international MBA in U.S. News rankings - Florida International University</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>These Are FL's Best Graduate Schools, U.S. News Says In New Ranking - Patch</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B11" t="n">
-        <v>56</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7419381141662598</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fuel price protests see traffic disruption on major road networks - Irish Farmers Journal</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>WATCH: Traffic chaos across Ireland as fuel protest convoys hit major routes - Extra.ie</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>57</v>
-      </c>
-      <c r="B12" t="n">
-        <v>59</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.7406620383262634</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LIVE as man dies and another injured after double stabbing in Primrose Hill - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>57</v>
-      </c>
-      <c r="B13" t="n">
-        <v>61</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8756085634231567</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Man, 21, dies after being stabbed at Primrose Hill viewpoint - Sky News</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>57</v>
-      </c>
-      <c r="B14" t="n">
-        <v>62</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.5336514711380005</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Man, 26, killed in triple stabbing outside Peckham nightclub pictured as two others fight for life - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>57</v>
-      </c>
-      <c r="B15" t="n">
-        <v>63</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8609005212783813</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Man, 21, stabbed to death at Primrose Hill beauty spot in London - The Telegraph</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>57</v>
-      </c>
-      <c r="B16" t="n">
-        <v>64</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.6760867834091187</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Police launch murder investigation after fatal stabbing at Primrose Hill viewpoint - The Independent</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>57</v>
-      </c>
-      <c r="B17" t="n">
-        <v>65</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.603789210319519</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Man, 21, dead and another wounded after double stabbing at London beauty spot - lbc.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>57</v>
-      </c>
-      <c r="B18" t="n">
-        <v>66</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.7322710156440735</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Primrose Hill: Police launch murder probe after man stabbed at popular London beauty spot - GB News</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>57</v>
-      </c>
-      <c r="B19" t="n">
-        <v>69</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.4953832030296326</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Man, 21, stabbed to death at iconic London beauty spot as second person injured &amp; murder probe launched - The Sun</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>57</v>
-      </c>
-      <c r="B20" t="n">
-        <v>71</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5161443948745728</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Man, 26, killed in triple stabbing outside Peckham nightclub named as two others fight for life - London Evening Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>57</v>
-      </c>
-      <c r="B21" t="n">
-        <v>72</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.8945730924606323</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Man, 21, dies after stabbing in Primrose Hill - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>57</v>
-      </c>
-      <c r="B22" t="n">
-        <v>75</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.460145890712738</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Man fighting for life among two in hospital after fatal Peckham stabbing - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>57</v>
-      </c>
-      <c r="B23" t="n">
-        <v>76</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.8945730924606323</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Man, 21, dies after stabbing in Primrose Hill - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>57</v>
-      </c>
-      <c r="B24" t="n">
-        <v>78</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.4845749139785767</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Forensics probe after man, 26, killed outside south east London nightclub - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>57</v>
-      </c>
-      <c r="B25" t="n">
-        <v>79</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5377892255783081</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Man, 21, fatally stabbed at Primrose Hill - BBC</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Everything we know as man killed in triple south east London nightclub stabbing - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>68</v>
-      </c>
-      <c r="B26" t="n">
-        <v>70</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.7595713138580322</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Boy shot dead, young man killed and 3 more stabbed in London Easter weekend horror - My London</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Four dead and several stabbed in GRIM Easter weekend across London - London Now</t>
+          <t>Anche la Cgil di Sondrio scende in piazza per il rilancio della sanità pubblica lombarda - sondriotoday.it</t>
         </is>
       </c>
     </row>
